--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1124,7 +1124,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4856-186-CM25</t>
+          <t>4455-217-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2249.1</v>
+        <v>11135.31</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1246,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4455-217-CM25</t>
+          <t>4856-186-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11135.31</v>
+        <v>2249.1</v>
       </c>
     </row>
     <row r="15">
@@ -1429,7 +1429,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4025-91-CM25</t>
+          <t>4083-248-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1449,17 +1449,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.262.800-4</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTUCO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5287.77</v>
+        <v>4673.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4083-248-CM25</t>
+          <t>4025-91-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.262.800-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE ANTUCO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4673.13</v>
+        <v>5287.77</v>
       </c>
     </row>
     <row r="19">
@@ -2714,7 +2714,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2408-4495-CM25</t>
+          <t>1057931-109-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.607.200-5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2769,13 +2769,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1903.27</v>
+        <v>10150.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4455-765-CM25</t>
+          <t>2408-4495-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>845.9</v>
+        <v>1903.27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057931-109-CM25</t>
+          <t>4455-765-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.607.200-5</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>DIRECCION SERVICIO DE SALUD TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>10150.8</v>
+        <v>845.9</v>
       </c>
     </row>
     <row r="41">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3537,7 +3537,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4060,7 +4060,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1456840-17-CM26</t>
+          <t>4493-122-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.981.460-6</t>
+          <t>69.150.502-2</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL RELONCAVÍ</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4115,13 +4115,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1173.34</v>
+        <v>4169.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4493-122-CM26</t>
+          <t>1057404-402-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4146,12 +4146,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.150.502-2</t>
+          <t>61.602.209-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Penco - Salud</t>
+          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4161,12 +4161,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>4169.02</v>
+        <v>2998.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057404-402-CM26</t>
+          <t>2410-54-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.209-1</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCO HOSPITAL DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>MSLI Latam Inc.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>880443249</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4237,13 +4237,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2998.8</v>
+        <v>72770.88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2410-54-CM26</t>
+          <t>4454-332-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>69.150.600-2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MSLI Latam Inc.</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>880443249</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4298,13 +4298,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>72770.88</v>
+        <v>2307.83</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4454-332-CM26</t>
+          <t>4856-134-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4314,27 +4314,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>69.150.600-2</t>
+          <t>69.160.700-3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI</t>
+          <t>I MUNICIPALIDAD DE TIRUA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2307.83</v>
+        <v>2548.98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4856-134-CM26</t>
+          <t>4238-132-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.160.700-3</t>
+          <t>69.160.202-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIRUA</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4420,13 +4420,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2548.98</v>
+        <v>19514.57</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4238-132-CM26</t>
+          <t>4079-211-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.160.202-8</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curanilahue - Salud</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4481,13 +4481,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>19514.57</v>
+        <v>7819.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4079-211-CM26</t>
+          <t>1057544-9434-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4502,22 +4502,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>61.607.202-1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>Intercity S.A.</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.826.830-9</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4542,13 +4542,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7819.73</v>
+        <v>1203.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057544-9434-CM26</t>
+          <t>1084156-411-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4563,22 +4563,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.607.202-1</t>
+          <t>65.181.672-6</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DE TALCAHUANO HOSPITAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4588,12 +4588,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Intercity S.A.</t>
+          <t>Netsus SpA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>96.826.830-9</t>
+          <t>76.288.338-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1203.6</v>
+        <v>9346.26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1084156-411-CM26</t>
+          <t>4083-257-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4619,27 +4619,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>65.181.672-6</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA ANDALIEN SUR</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>NETSUS SPA</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.288.338-4</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>9346.26</v>
+        <v>5247.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4083-257-CM26</t>
+          <t>3796-350-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4725,13 +4725,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5247.9</v>
+        <v>35078.96</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3796-350-CM26</t>
+          <t>2360-474-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4746,22 +4746,22 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.150.800-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4786,13 +4786,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>35078.96</v>
+        <v>7607.1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2360-474-CM26</t>
+          <t>2421-857-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4807,7 +4807,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4817,12 +4817,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.150.800-5</t>
+          <t>69.256.900-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCAHUANO</t>
+          <t>I MUNICIPALIDAD DE CONCEPCION</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4832,12 +4832,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPTIMIZA SEGURIDAD SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.854.651-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4847,13 +4847,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>7607.1</v>
+        <v>36235.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2421-857-CM26</t>
+          <t>2098-1687-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4868,22 +4868,22 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>69.256.900-8</t>
+          <t>61.602.211-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dirección de Administración de Salud Municipal</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>OPTIMIZA SEGURIDAD SPA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.854.651-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4908,13 +4908,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>36235.5</v>
+        <v>74302.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2098-1687-CM26</t>
+          <t>4189-468-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4929,22 +4929,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.602.211-3</t>
+          <t>69.160.300-8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE LEBU</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4969,13 +4969,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>74302.77</v>
+        <v>15079.44</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4189-468-CM26</t>
+          <t>3606-145-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.160.300-8</t>
+          <t>61.967.400-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LEBU</t>
+          <t>I MUNICIPALIDAD DE MULCHEN</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>15079.44</v>
+        <v>4878.64</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3606-145-CM26</t>
+          <t>4494-608-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.967.400-6</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MULCHEN</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5091,13 +5091,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4878.64</v>
+        <v>35481.04</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4358-163-CM26</t>
+          <t>4414-1161-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.170.701-6</t>
+          <t>69.160.100-5</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+          <t>I MUNICIPALIDAD DE ARAUCO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECNOLOGIA BS SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.852.815-2</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5152,13 +5152,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>7061.04</v>
+        <v>29687.88</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4494-608-CM26</t>
+          <t>2408-851-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5168,27 +5168,27 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TECNOLOGIA BS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.852.815-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5213,13 +5213,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>35481.04</v>
+        <v>42830.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4414-1161-CM26</t>
+          <t>2409-1109-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.160.100-5</t>
+          <t>69.170.101-8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARAUCO</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5274,7 +5274,68 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>29687.88</v>
+        <v>22175.65</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1214105-13-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>65.191.629-1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Corporación Municipal de Deportes y Recreación Talcahuano</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>EMPRESA NACIONAL DE TELECOMUNICACIONES S A</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>92.580.000-7</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>4812.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
@@ -684,7 +684,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +940,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1005,11 @@
           <t>76.334.381-2</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1070,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1135,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1200,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1265,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1452,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1708,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1773,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1838,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1903,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1968,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2033,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2098,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2163,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2228,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2293,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2419,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2484,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2549,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2740,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2805,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2870,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2935,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3000,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +3065,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3130,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3195,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3260,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3325,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3512,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3577,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3642,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3620,7 +3772,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3681,7 +3837,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3902,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3864,7 +4028,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4154,11 @@
           <t>76.083.145-k</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4047,7 +4219,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4108,7 +4284,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4291,7 +4471,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4597,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4662,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4727,11 @@
           <t>96.826.830-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4792,11 @@
           <t>76.288.338-4</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4918,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +4983,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5109,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4962,7 +5174,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5023,7 +5239,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5084,7 +5304,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5145,7 +5369,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5434,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5267,7 +5499,11 @@
           <t>76.852.815-2</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5328,7 +5564,11 @@
           <t>92.580.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
+++ b/docs/oc-regiones/licencia-de-software-de-ofimatica/biobio.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5578,6 +5578,71 @@
         <v>4812.36</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4358-205-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-11-LR24</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.170.701-6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>XMS TECHNOLOGIES S.A.</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>76.083.145-k</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>4308.94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
